--- a/Rodier-Finding-gemma3-bert-scores.xlsx
+++ b/Rodier-Finding-gemma3-bert-scores.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="53">
   <si>
     <t>DOCUMENT</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Did the coroner evaluate the adequacy of supervision, treatment, or care provided? Explain the conclusion.</t>
   </si>
   <si>
+    <t>Does this case highlight any broader patterns or lessons relevant to public safety or institutional care?</t>
+  </si>
+  <si>
     <t xml:space="preserve">The deceased was Frank Edward Rodier </t>
   </si>
   <si>
@@ -124,6 +127,9 @@
     <t xml:space="preserve">Not applicable in this case; the death occurred during a recreational activity at sea, not under institutional supervision or care </t>
   </si>
   <si>
+    <t>Yes. The Rodier case underscores a broader public safety lesson about the persistent dangers of rock fishing and the need for preventive measures at hazardous coastal sites. The coroner observed that while Western Australia has since introduced safety improvements such as life rings and tether points at popular rock fishing locations, remote areas like Quobba Station remain perilous and largely unmonitored. The finding highlights how environmental risks, rather than institutional failures, were central, emphasizing the importance of sustained public education, signage, and infrastructure to reduce fatalities from recreational fishing accidents</t>
+  </si>
+  <si>
     <t>Frank Edward Rodier was the deceased.</t>
   </si>
   <si>
@@ -133,40 +139,47 @@
     <t>The death occurred in the waters of the Indian Ocean off Quobba Station near Red Bluff, Carnarvon.</t>
   </si>
   <si>
-    <t>The cause of death remains unascertained. The report states: “Accordingly, his cause of death must remain unascertained.”</t>
-  </si>
-  <si>
-    <t>Sarah Helen Linton, Deputy State Coroner.</t>
-  </si>
-  <si>
-    <t>According to the provided text, Frank Rodier died in the sea on 25, 1975, after being washed off the rocks while fishing with friends. The coroner determined the death was likely an accident, but couldn’t determine the exact cause of death, only noting a possible contribution from injuries sustained from the rocks.</t>
-  </si>
-  <si>
-    <t>Frank had some slight impairments, such as speech.</t>
+    <t>According to the provided text, the cause of death remains unascertained. The coroner determined that Frank Rodier died in the sea after being washed off the rocks while fishing, but could not determine whether it was due to injuries sustained from the rocks or if the injuries contributed to his death.</t>
+  </si>
+  <si>
+    <t>Sarah Helen Linton, Deputy State Coroner</t>
+  </si>
+  <si>
+    <t>According to the provided text, Frank Rodier died in the sea on 25 1975 after being washed off the rocks while fishing with friends. The report indicates he sustained injuries from the rocks, and his cause of death remains unascertained, but the manner of death was determined to be an accident.</t>
+  </si>
+  <si>
+    <t>According to the provided context, Frank had “some slight impairments, such as speech.” However, he had no known medical conditions that would have shortened his life span.</t>
   </si>
   <si>
     <t>Detective Senior Constable Wold and Senior Constable C Robertson testified or assisted in the inquest.</t>
   </si>
   <si>
-    <t>The provided context does not state whether Frank was considered a “person held in care” under the Coroners Act. It only indicates that the Acting State Coroner directed a police investigation based on a suspicion of death.</t>
-  </si>
-  <si>
-    <t>The provided context does not include any toxicology findings or information regarding substances or drugs in the body. It only states that a direction was made to investigate a suspected death under the Coroners Act 1996 (WA).</t>
-  </si>
-  <si>
-    <t>Based on the provided information, the Acting State Coroner, in August 2023, determined there was reasonable cause to suspect Frank’s death and that it was a reportable death. Consequently, the Coroner directed the Commissioner of Police to investigate the suspected death, as outlined in section 23(1) of the Coroners Act 1996 (WA). This action was taken following information provided by the WA Police.</t>
-  </si>
-  <si>
-    <t>The provided context does not state whether the coroner made recommendations for future prevention. It only outlines the initial determination that Frank’s death was a reportable death and the subsequent direction for investigation.</t>
-  </si>
-  <si>
-    <t>Based on the provided text, here’s a differentiation between the immediate cause of death and contributing factors for Frank Rodier’s death:
-*   **Immediate Cause of Death:** The report states Frank died “in the sea after he was washed off the rocks while fishing with friends.” This is considered the immediate trigger for his death.
-*   **Contributing Factors:** The report notes that “I cannot exclude the possibility that he died from injuries he sustained from the rocks, or that injury at least contributed to his death.” This identifies the injuries from the rocks as a potential contributing factor to his demise. The report also mentions an “impediment; associated with events at the time of his birth.” 
-**In essence, the immediate cause was the fall and subsequent drowning, while injuries from the rocks are considered a contributing factor alongside the birth-related impediment.**</t>
-  </si>
-  <si>
-    <t>The provided context information does not indicate whether the coroner evaluated the adequacy of supervision, treatment, or care provided. It only states that the coroner determined there was reasonable cause to suspect Frank’s death and directed a police investigation based on information from the WA Police in August 2023. It focuses solely on the initial suspicion of death and the subsequent investigative direction, without detailing any assessment of the circumstances surrounding the death, including care or supervision.</t>
+    <t>The provided context does not state whether Frank was considered a “person held in care” under the Coroners Act. It only outlines the circumstances leading to the investigation of his suspected death, initiated by the WA Police and directed by the Acting State Coroner.</t>
+  </si>
+  <si>
+    <t>The provided context does not include any toxicology findings. It only states that a direction was made to investigate a suspected death based on information from the WA Police. There is no mention of any substance or drug analysis.</t>
+  </si>
+  <si>
+    <t>Based on the provided context, the Acting State Coroner, following information from the WA Police in August 2023, determined there was reasonable cause to suspect Frank’s death was a reportable death. Consequently, a direction was issued to the Commissioner of Police to investigate the suspected death under Section 23(1) of the Coroners Act 1996 (WA). This action was taken due to the evidence suggesting a reportable death.</t>
+  </si>
+  <si>
+    <t>The provided context does not state whether the coroner made any recommendations for future prevention. It only indicates that the coroner directed the Commissioner of Police to investigate the suspected death.</t>
+  </si>
+  <si>
+    <t>According to the provided text, the immediate cause of death for Frank Rodier is that he “died on 25 [year] 1975 in the sea after he was washed off the rocks while fishing with friends.”
+However, the report states that he “cannot exclude the possibility that he died from injuries he sustained from the rocks, or that injury at least contributed to his death.” This indicates that injuries sustained from the rocks were a contributing factor to his death, but the precise cause of death remains “unascertained.”</t>
+  </si>
+  <si>
+    <t>The provided context information does not indicate whether the coroner evaluated the adequacy of supervision, treatment, or care provided. It only states that the coroner determined there was reasonable cause to suspect Frank’s death and directed a police investigation based on information from the WA Police in August 2023. It focuses on the initial suspicion of death and the subsequent investigative direction, without detailing any assessment of the circumstances surrounding the death, including care or supervision.</t>
+  </si>
+  <si>
+    <t>Based on the provided context, this case highlights several broader patterns and lessons relevant to public safety and institutional care:
+*   **Delayed Investigation &amp; Closure:** The significant time elapsed since Frank’s disappearance (1975 to 2023) demonstrates the challenges of investigating missing persons cases, particularly when initial investigations are incomplete or lack sufficient resources. This points to the need for proactive, sustained investigation efforts, not just reactive responses.
+*   **Importance of Ongoing Review:** The 2006 review and subsequent 2015 and 2023 enquiries underscore the importance of periodically revisiting cold cases. New investigative techniques, forensic advancements, and renewed resources could potentially uncover crucial information.
+*   **Systemic Issues in Initial Reporting:** The fact that the initial report was made 50 years after the disappearance suggests potential weaknesses in initial reporting mechanisms and the speed with which cases are escalated to the police.
+*   **Need for Institutional Memory:** The case emphasizes the critical role of institutional memory within law enforcement agencies. The 2015 and 2023 reviews suggest that information from older investigations might have been lost or overlooked, delaying a proper assessment.
+*   **Potential for Vulnerable Individuals:** While the case doesn't explicitly state it, a long-term missing person case raises questions about the circumstances surrounding Frank's disappearance and potential vulnerabilities he may have had. This highlights the need for institutions (police, social services) to be vigilant in identifying and supporting individuals at risk.
+In essence, this case serves as a reminder of the complexities of missing persons investigations, the importance of sustained efforts, and the need for robust systems to ensure timely and effective investigations, ultimately contributing to public safety.</t>
   </si>
 </sst>
 </file>
@@ -524,7 +537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -558,10 +571,10 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2">
         <v>0.9384459853172302</v>
@@ -581,10 +594,10 @@
         <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>0.9117177724838257</v>
@@ -604,10 +617,10 @@
         <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4">
         <v>0.9349055886268616</v>
@@ -627,19 +640,19 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E5">
-        <v>0.8521266579627991</v>
+        <v>0.8541771173477173</v>
       </c>
       <c r="F5">
-        <v>0.8507088422775269</v>
+        <v>0.8770735859870911</v>
       </c>
       <c r="G5">
-        <v>0.8514171242713928</v>
+        <v>0.8654739260673523</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -650,19 +663,19 @@
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>0.9924659729003906</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0.9916324615478516</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0.9920490384101868</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -673,19 +686,19 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7">
-        <v>0.8620737195014954</v>
+        <v>0.8668072819709778</v>
       </c>
       <c r="F7">
-        <v>0.8638648390769958</v>
+        <v>0.870517373085022</v>
       </c>
       <c r="G7">
-        <v>0.8629683256149292</v>
+        <v>0.8686583042144775</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -696,19 +709,19 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8">
-        <v>0.8997482657432556</v>
+        <v>0.8862928748130798</v>
       </c>
       <c r="F8">
-        <v>0.8478087782859802</v>
+        <v>0.8874114751815796</v>
       </c>
       <c r="G8">
-        <v>0.8730066418647766</v>
+        <v>0.8868518471717834</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -719,10 +732,10 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E9">
         <v>0.9057745933532715</v>
@@ -742,19 +755,19 @@
         <v>16</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10">
-        <v>0.8452259302139282</v>
+        <v>0.8394547700881958</v>
       </c>
       <c r="F10">
-        <v>0.8660017251968384</v>
+        <v>0.866795539855957</v>
       </c>
       <c r="G10">
-        <v>0.8554877042770386</v>
+        <v>0.8529060482978821</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -765,19 +778,19 @@
         <v>17</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E11">
-        <v>0.8255354762077332</v>
+        <v>0.8444669842720032</v>
       </c>
       <c r="F11">
-        <v>0.8917224407196045</v>
+        <v>0.8904483914375305</v>
       </c>
       <c r="G11">
-        <v>0.8573534488677979</v>
+        <v>0.866848349571228</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -788,19 +801,19 @@
         <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E12">
-        <v>0.8293969631195068</v>
+        <v>0.8285360336303711</v>
       </c>
       <c r="F12">
-        <v>0.8301089406013489</v>
+        <v>0.8279961347579956</v>
       </c>
       <c r="G12">
-        <v>0.8297528624534607</v>
+        <v>0.8282659649848938</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -811,19 +824,19 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E13">
-        <v>0.8524782061576843</v>
+        <v>0.8571929931640625</v>
       </c>
       <c r="F13">
-        <v>0.84672611951828</v>
+        <v>0.8438748121261597</v>
       </c>
       <c r="G13">
-        <v>0.8495924472808838</v>
+        <v>0.8504817485809326</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -834,19 +847,19 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14">
-        <v>0.806526780128479</v>
+        <v>0.8238552808761597</v>
       </c>
       <c r="F14">
-        <v>0.8354616165161133</v>
+        <v>0.8525538444519043</v>
       </c>
       <c r="G14">
-        <v>0.8207392692565918</v>
+        <v>0.8379589319229126</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -857,19 +870,42 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E15">
-        <v>0.8267449140548706</v>
+        <v>0.8274308443069458</v>
       </c>
       <c r="F15">
-        <v>0.8443306088447571</v>
+        <v>0.8445773124694824</v>
       </c>
       <c r="G15">
-        <v>0.8354451656341553</v>
+        <v>0.8359161019325256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16">
+        <v>0.8128820657730103</v>
+      </c>
+      <c r="F16">
+        <v>0.8448825478553772</v>
+      </c>
+      <c r="G16">
+        <v>0.8285734057426453</v>
       </c>
     </row>
   </sheetData>
